--- a/data/1000-seed-weight.xlsx
+++ b/data/1000-seed-weight.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uwy-my.sharepoint.com/personal/sbhatta4_uwyo_edu/Documents/1UW/Extension/Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD59A3AB-4148-4929-AB5F-ED92003E0E8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{FD59A3AB-4148-4929-AB5F-ED92003E0E8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A555771A-8A04-43EC-9FBC-F004FA08030D}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{7C6D874A-C915-4490-B63D-FC02FF4CC0A4}"/>
   </bookViews>
@@ -39,17 +39,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
   <si>
     <t xml:space="preserve">Forage Species </t>
   </si>
   <si>
-    <t>1000 seed weight (kg)</t>
-  </si>
-  <si>
-    <t>1000 seed weight (lb)</t>
-  </si>
-  <si>
     <t>Alfalfa</t>
   </si>
   <si>
@@ -237,6 +231,9 @@
   </si>
   <si>
     <t>Western wheatgrass</t>
+  </si>
+  <si>
+    <t>1000 seed weight (g)</t>
   </si>
 </sst>
 </file>
@@ -608,716 +605,523 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB3D5D81-B1CE-4D6B-87C2-05C0B4E6BB66}">
-  <dimension ref="A1:C64"/>
+  <dimension ref="A1:B64"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25.7265625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B2">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B2">
-        <v>2E-3</v>
-      </c>
-      <c r="C2">
-        <v>4.4052863436123352E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="B4">
+        <v>13.888888888888888</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B3">
-        <v>6.6666666666666664E-4</v>
-      </c>
-      <c r="C3">
-        <v>1.4705882352941176E-3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="B5">
+        <v>1.2269938650306749</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B4">
-        <v>1.3888888888888888E-2</v>
-      </c>
-      <c r="C4">
-        <v>3.0303030303030304E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="B6">
+        <v>3.7037037037037037</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="B5">
-        <v>1.2269938650306749E-3</v>
-      </c>
-      <c r="C5">
-        <v>2.7027027027027029E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+      <c r="B7">
+        <v>22.727272727272727</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="B6">
-        <v>3.7037037037037038E-3</v>
-      </c>
-      <c r="C6">
-        <v>8.1967213114754103E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+      <c r="B8">
+        <v>1.8115942028985508</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B7">
-        <v>2.2727272727272728E-2</v>
-      </c>
-      <c r="C7">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+      <c r="B9">
+        <v>1.6501650165016502</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>9</v>
       </c>
-      <c r="B8">
-        <v>1.8115942028985507E-3</v>
-      </c>
-      <c r="C8">
-        <v>4.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+      <c r="B10">
+        <v>1.6666666666666667</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>10</v>
       </c>
-      <c r="B9">
-        <v>1.6501650165016502E-3</v>
-      </c>
-      <c r="C9">
-        <v>3.6363636363636364E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+      <c r="B11">
+        <v>15.151515151515152</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>11</v>
       </c>
-      <c r="B10">
-        <v>1.6666666666666668E-3</v>
-      </c>
-      <c r="C10">
-        <v>3.6764705882352941E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+      <c r="B12">
+        <v>1.7543859649122808</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>12</v>
       </c>
-      <c r="B11">
-        <v>1.5151515151515152E-2</v>
-      </c>
-      <c r="C11">
-        <v>3.3333333333333333E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+      <c r="B13">
+        <v>0.56689342403628118</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>13</v>
       </c>
-      <c r="B12">
-        <v>1.7543859649122807E-3</v>
-      </c>
-      <c r="C12">
-        <v>3.8610038610038611E-3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+      <c r="B14">
+        <v>0.87489063867016625</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>14</v>
       </c>
-      <c r="B13">
-        <v>5.6689342403628119E-4</v>
-      </c>
-      <c r="C13">
-        <v>1.25E-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+      <c r="B15">
+        <v>7.518796992481203</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>15</v>
       </c>
-      <c r="B14">
-        <v>8.7489063867016625E-4</v>
-      </c>
-      <c r="C14">
-        <v>1.9267822736030828E-3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+      <c r="B16">
+        <v>3.6900369003690034</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>16</v>
       </c>
-      <c r="B15">
-        <v>7.5187969924812026E-3</v>
-      </c>
-      <c r="C15">
-        <v>1.6666666666666666E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+      <c r="B17">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
         <v>17</v>
       </c>
-      <c r="B16">
-        <v>3.6900369003690036E-3</v>
-      </c>
-      <c r="C16">
-        <v>8.130081300813009E-3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+      <c r="B18">
+        <v>3.1545741324921135</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>18</v>
       </c>
-      <c r="B17">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="C17">
-        <v>1.1025358324145535E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+      <c r="B19">
+        <v>3.0211480362537766</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>19</v>
       </c>
-      <c r="B18">
-        <v>3.1545741324921135E-3</v>
-      </c>
-      <c r="C18">
-        <v>6.9444444444444441E-3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+      <c r="B20">
+        <v>0.62656641604010022</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
         <v>20</v>
       </c>
-      <c r="B19">
-        <v>3.0211480362537764E-3</v>
-      </c>
-      <c r="C19">
-        <v>6.6666666666666671E-3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+      <c r="B21">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
         <v>21</v>
       </c>
-      <c r="B20">
-        <v>6.2656641604010022E-4</v>
-      </c>
-      <c r="C20">
-        <v>1.3804527885146328E-3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
+      <c r="B22">
+        <v>4.5662100456620998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
         <v>22</v>
       </c>
-      <c r="B21">
-        <v>2.0000000000000001E-4</v>
-      </c>
-      <c r="C21">
-        <v>4.4091710758377423E-4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
+      <c r="B23">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
         <v>23</v>
       </c>
-      <c r="B22">
-        <v>4.5662100456621002E-3</v>
-      </c>
-      <c r="C22">
-        <v>1.0101010101010102E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
+      <c r="B24">
+        <v>0.93632958801498123</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
         <v>24</v>
       </c>
-      <c r="B23">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="C23">
-        <v>8.8495575221238937E-3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
+      <c r="B25">
+        <v>0.57703404500865552</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
         <v>25</v>
       </c>
-      <c r="B24">
-        <v>9.3632958801498128E-4</v>
-      </c>
-      <c r="C24">
-        <v>2.0661157024793389E-3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
+      <c r="B26">
+        <v>1.2106537530266344</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
         <v>26</v>
       </c>
-      <c r="B25">
-        <v>5.7703404500865547E-4</v>
-      </c>
-      <c r="C25">
-        <v>1.2722646310432571E-3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
+      <c r="B27">
+        <v>2.3364485981308412</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
         <v>27</v>
       </c>
-      <c r="B26">
-        <v>1.2106537530266344E-3</v>
-      </c>
-      <c r="C26">
-        <v>2.6666666666666666E-3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
+      <c r="B28">
+        <v>5.1546391752577323</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
         <v>28</v>
       </c>
-      <c r="B27">
-        <v>2.3364485981308409E-3</v>
-      </c>
-      <c r="C27">
-        <v>5.1546391752577319E-3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
+      <c r="B29">
+        <v>0.14374011786689664</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
         <v>29</v>
       </c>
-      <c r="B28">
-        <v>5.1546391752577319E-3</v>
-      </c>
-      <c r="C28">
-        <v>1.1363636363636364E-2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
+      <c r="B30">
+        <v>1.7331022530329288</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
         <v>30</v>
       </c>
-      <c r="B29">
-        <v>1.4374011786689664E-4</v>
-      </c>
-      <c r="C29">
-        <v>3.1685678073510771E-4</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
+      <c r="B31">
+        <v>2.5062656641604009</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
         <v>31</v>
       </c>
-      <c r="B30">
-        <v>1.7331022530329288E-3</v>
-      </c>
-      <c r="C30">
-        <v>3.8167938931297708E-3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
+      <c r="B32">
+        <v>3.8439952949497589</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
         <v>32</v>
       </c>
-      <c r="B31">
-        <v>2.5062656641604009E-3</v>
-      </c>
-      <c r="C31">
-        <v>5.5248618784530384E-3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
+      <c r="B33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
         <v>33</v>
       </c>
-      <c r="B32">
-        <v>3.8439952949497589E-3</v>
-      </c>
-      <c r="C32">
-        <v>8.4745762711864406E-3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
+      <c r="B34">
+        <v>10.256410256410257</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
         <v>34</v>
       </c>
-      <c r="B33">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="C33">
-        <v>1.098901098901099E-2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
+      <c r="B35">
+        <v>5.6657223796034</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
         <v>35</v>
       </c>
-      <c r="B34">
-        <v>1.0256410256410256E-2</v>
-      </c>
-      <c r="C34">
-        <v>2.2727272727272728E-2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
+      <c r="B36">
+        <v>1.996007984031936</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
         <v>36</v>
       </c>
-      <c r="B35">
-        <v>5.6657223796033997E-3</v>
-      </c>
-      <c r="C35">
-        <v>1.2500000000000001E-2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
+      <c r="B37">
+        <v>0.29002320185614849</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
         <v>37</v>
       </c>
-      <c r="B36">
-        <v>1.996007984031936E-3</v>
-      </c>
-      <c r="C36">
-        <v>4.4052863436123352E-3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
+      <c r="B38">
+        <v>0.20833333333333334</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
         <v>38</v>
       </c>
-      <c r="B37">
-        <v>2.9002320185614848E-4</v>
-      </c>
-      <c r="C37">
-        <v>6.3938618925831207E-4</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
+      <c r="B39">
+        <v>1.890359168241966</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
         <v>39</v>
       </c>
-      <c r="B38">
-        <v>2.0833333333333335E-4</v>
-      </c>
-      <c r="C38">
-        <v>4.5934772622875517E-4</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
+      <c r="B40">
+        <v>5.2356020942408383</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
         <v>40</v>
       </c>
-      <c r="B39">
-        <v>1.890359168241966E-3</v>
-      </c>
-      <c r="C39">
-        <v>4.1666666666666666E-3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
+      <c r="B41">
+        <v>1.9723865877712032</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
         <v>41</v>
       </c>
-      <c r="B40">
-        <v>5.235602094240838E-3</v>
-      </c>
-      <c r="C40">
-        <v>1.1494252873563218E-2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
+      <c r="B42">
+        <v>0.78740157480314954</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
         <v>42</v>
       </c>
-      <c r="B41">
-        <v>1.9723865877712033E-3</v>
-      </c>
-      <c r="C41">
-        <v>4.3478260869565218E-3</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
+      <c r="B43">
+        <v>3.2894736842105261</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
         <v>43</v>
       </c>
-      <c r="B42">
-        <v>7.874015748031496E-4</v>
-      </c>
-      <c r="C42">
-        <v>1.736111111111111E-3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
+      <c r="B44">
+        <v>3.125</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
         <v>44</v>
       </c>
-      <c r="B43">
-        <v>3.2894736842105261E-3</v>
-      </c>
-      <c r="C43">
-        <v>7.246376811594203E-3</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
+      <c r="B45">
+        <v>1.0615711252653928</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
         <v>45</v>
       </c>
-      <c r="B44">
-        <v>3.1250000000000002E-3</v>
-      </c>
-      <c r="C44">
-        <v>6.8965517241379309E-3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
+      <c r="B46">
+        <v>1.8867924528301887</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
         <v>46</v>
       </c>
-      <c r="B45">
-        <v>1.0615711252653928E-3</v>
-      </c>
-      <c r="C45">
-        <v>2.34192037470726E-3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
+      <c r="B47">
+        <v>5.6818181818181817</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
         <v>47</v>
       </c>
-      <c r="B46">
-        <v>1.8867924528301887E-3</v>
-      </c>
-      <c r="C46">
-        <v>4.1666666666666666E-3</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
+      <c r="B48">
+        <v>9.3720712277413312E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
         <v>48</v>
       </c>
-      <c r="B47">
-        <v>5.681818181818182E-3</v>
-      </c>
-      <c r="C47">
-        <v>1.2500000000000001E-2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
+      <c r="B49">
+        <v>0.84317032040472173</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
         <v>49</v>
       </c>
-      <c r="B48">
-        <v>9.372071227741331E-5</v>
-      </c>
-      <c r="C48">
-        <v>2.0661157024793388E-4</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
+      <c r="B50">
+        <v>0.96061479346781942</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
         <v>50</v>
       </c>
-      <c r="B49">
-        <v>8.4317032040472171E-4</v>
-      </c>
-      <c r="C49">
-        <v>1.8587360594795538E-3</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
+      <c r="B51">
+        <v>1.6666666666666667</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
         <v>51</v>
       </c>
-      <c r="B50">
-        <v>9.6061479346781938E-4</v>
-      </c>
-      <c r="C50">
-        <v>2.1186440677966102E-3</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
+      <c r="B52">
+        <v>2.7932960893854748</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
         <v>52</v>
       </c>
-      <c r="B51">
-        <v>1.6666666666666668E-3</v>
-      </c>
-      <c r="C51">
-        <v>3.6764705882352941E-3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
+      <c r="B53">
+        <v>0.66755674232309747</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
         <v>53</v>
       </c>
-      <c r="B52">
-        <v>2.7932960893854749E-3</v>
-      </c>
-      <c r="C52">
-        <v>6.1728395061728392E-3</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
+      <c r="B54">
+        <v>2.3752969121140142</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
         <v>54</v>
       </c>
-      <c r="B53">
-        <v>6.6755674232309744E-4</v>
-      </c>
-      <c r="C53">
-        <v>1.4705882352941176E-3</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
+      <c r="B55">
+        <v>3.3557046979865772</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
         <v>55</v>
       </c>
-      <c r="B54">
-        <v>2.3752969121140144E-3</v>
-      </c>
-      <c r="C54">
-        <v>5.235602094240838E-3</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
+      <c r="B56">
+        <v>3.1746031746031744</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
         <v>56</v>
       </c>
-      <c r="B55">
-        <v>3.3557046979865771E-3</v>
-      </c>
-      <c r="C55">
-        <v>7.4074074074074077E-3</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
+      <c r="B57">
+        <v>2.8248587570621471</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
         <v>57</v>
       </c>
-      <c r="B56">
-        <v>3.1746031746031746E-3</v>
-      </c>
-      <c r="C56">
-        <v>6.993006993006993E-3</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
+      <c r="B58">
+        <v>1.1655011655011656</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
         <v>58</v>
       </c>
-      <c r="B57">
-        <v>2.8248587570621469E-3</v>
-      </c>
-      <c r="C57">
-        <v>6.2500000000000003E-3</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
+      <c r="B59">
+        <v>2.2026431718061676</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
         <v>59</v>
       </c>
-      <c r="B58">
-        <v>1.1655011655011655E-3</v>
-      </c>
-      <c r="C58">
-        <v>2.5706940874035988E-3</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
+      <c r="B60">
+        <v>6.024096385542169</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
         <v>60</v>
       </c>
-      <c r="B59">
-        <v>2.2026431718061676E-3</v>
-      </c>
-      <c r="C59">
-        <v>4.8543689320388345E-3</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
+      <c r="B61">
+        <v>0.39001560062402496</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
         <v>61</v>
       </c>
-      <c r="B60">
-        <v>6.024096385542169E-3</v>
-      </c>
-      <c r="C60">
-        <v>1.3333333333333334E-2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
+      <c r="B62">
+        <v>0.27777777777777779</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
         <v>62</v>
       </c>
-      <c r="B61">
-        <v>3.9001560062402497E-4</v>
-      </c>
-      <c r="C61">
-        <v>8.598452278589854E-4</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
+      <c r="B63">
+        <v>7.9744816586921843</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
         <v>63</v>
       </c>
-      <c r="B62">
-        <v>2.7777777777777778E-4</v>
-      </c>
-      <c r="C62">
-        <v>6.1236987140232701E-4</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
-        <v>64</v>
-      </c>
-      <c r="B63">
-        <v>7.9744816586921844E-3</v>
-      </c>
-      <c r="C63">
-        <v>1.7543859649122806E-2</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
-        <v>65</v>
-      </c>
       <c r="B64">
-        <v>3.952569169960474E-3</v>
-      </c>
-      <c r="C64">
-        <v>8.6956521739130436E-3</v>
+        <v>3.9525691699604741</v>
       </c>
     </row>
   </sheetData>
